--- a/중국라벨_판매현황_광고테스트.xlsx
+++ b/중국라벨_판매현황_광고테스트.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="판매현황 (주별·월별)" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="광고 입찰가 테스트" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="광고현황" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="367">
   <si>
     <r>
       <rPr>
@@ -789,7 +789,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(5/25 ~ 10/6 </t>
+      <t xml:space="preserve">(5/25 ~ 10/8 </t>
     </r>
     <r>
       <rPr>
@@ -1332,7 +1332,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/9~10/6 </t>
+      <t xml:space="preserve">9/11~10/8 </t>
     </r>
     <r>
       <rPr>
@@ -2232,7 +2232,7 @@
     <t xml:space="preserve">전체 합계</t>
   </si>
   <si>
-    <t xml:space="preserve">5/25 ~ 10/6</t>
+    <t xml:space="preserve">5/25 ~ 10/8</t>
   </si>
   <si>
     <r>
@@ -4622,6 +4622,12 @@
       </rPr>
       <t xml:space="preserve">코스모스몰</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">      10/7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      10/8</t>
   </si>
   <si>
     <r>
@@ -4767,7 +4773,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">쇼핑검색 광고 입찰가 테스트 </t>
+      <t xml:space="preserve">쇼핑검색 광고현황 — 광고비 </t>
     </r>
     <r>
       <rPr>
@@ -4778,7 +4784,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(9/28 ~ 10/6)</t>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입찰가 테스트</t>
     </r>
   </si>
   <si>
@@ -5496,7 +5512,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">100*100</t>
+      <t xml:space="preserve">80*70 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100*100)</t>
     </r>
   </si>
   <si>
@@ -5743,7 +5776,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">테스트 기간 판매 변화 </t>
+      <t xml:space="preserve">광고비 현황 </t>
     </r>
     <r>
       <rPr>
@@ -5764,7 +5797,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">테스트 전 </t>
+      <t xml:space="preserve">라벨 소재 </t>
     </r>
     <r>
       <rPr>
@@ -5775,7 +5808,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
@@ -5785,7 +5818,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일 </t>
+      <t xml:space="preserve">네이버 검색광고 리포트 </t>
     </r>
     <r>
       <rPr>
@@ -5796,7 +5829,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vs </t>
+      <t xml:space="preserve">10/8 16:57 </t>
     </r>
     <r>
       <rPr>
@@ -5806,7 +5839,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">테스트 </t>
+      <t xml:space="preserve">다운로드</t>
     </r>
     <r>
       <rPr>
@@ -5817,8 +5850,1221 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">광고 소재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(VAT </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">입찰가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">품질
+지수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">노출수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">클릭수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">클릭률</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평균 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPC
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">광고비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전환수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전환매출</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고수익률
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전환매출</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유포지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30*15 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유포라벨</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클릭당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,370</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매가의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67%. 46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클릭에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 썼는데 전환은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6,140</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입찰가를 낮추거나 소재 점검 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60*40 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트라벨</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전환매출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구매완료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 중 효율이 가장 좋음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감열지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80*70 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100*100 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감열라벨</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전환매출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전환 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구매완료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공통</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기성라벨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감열</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출 적고 클릭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기성라벨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감열</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클릭 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35*20 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입찰가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">650</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">301, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클릭 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라벨 소재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파란 글씨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리포트 값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회 기간은 리포트 파일에 표시되지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전환은 네이버 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광고 클릭 후 구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이라 판매현황 기록과 다를 수 있습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -5827,7 +7073,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일</t>
+      <t xml:space="preserve">테스트 기간 판매 변화 </t>
     </r>
     <r>
       <rPr>
@@ -5838,6 +7084,90 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테스트 전 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F2A44"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -5987,7 +7317,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">100*100</t>
+      <t xml:space="preserve">80*70 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100*100)</t>
     </r>
   </si>
   <si>
@@ -6312,7 +7659,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">100*100: </t>
+      <t xml:space="preserve">80*70 (</t>
     </r>
     <r>
       <rPr>
@@ -6321,6 +7668,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">옵션 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100*100): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">전문몰 </t>
     </r>
     <r>
@@ -6407,7 +7773,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -6426,7 +7792,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">17</t>
     </r>
     <r>
       <rPr>
@@ -6797,9 +8163,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">입찰가</t>
-  </si>
-  <si>
     <t xml:space="preserve">조사 횟수</t>
   </si>
   <si>
@@ -8364,7 +9727,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">100*100</t>
+      <t xml:space="preserve">80*70 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100*100)</t>
     </r>
   </si>
   <si>
@@ -9024,13 +10408,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="#,##0;\-#,##0;&quot;-원&quot;"/>
-    <numFmt numFmtId="168" formatCode="\+#,##0;\-#,##0;0"/>
-    <numFmt numFmtId="169" formatCode="0\회"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="170" formatCode="\+#,##0;\-#,##0;0"/>
+    <numFmt numFmtId="171" formatCode="0\회"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -9223,7 +10609,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9258,6 +10644,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF1D6"/>
         <bgColor rgb="FFF2F3F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -9323,7 +10715,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="72">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9500,11 +10892,75 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9516,7 +10972,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9614,7 +11070,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF2F3F5"/>
       <rgbColor rgb="FFD6DFEE"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFAFAFA"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -9821,7 +11277,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V134"/>
+  <dimension ref="A1:V136"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="2" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -9874,10 +11330,10 @@
         <v>337</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
@@ -9897,10 +11353,10 @@
         <v>288</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>3</v>
@@ -9946,11 +11402,11 @@
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">D5+D6+D7</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">E5+E6+E7</f>
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">F5+F6+F7</f>
@@ -10016,10 +11472,10 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>2</v>
@@ -10029,15 +11485,15 @@
       </c>
       <c r="I13" s="12" t="n">
         <f aca="false">C13+E13+G13</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="12" t="n">
         <f aca="false">D13+F13+H13</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="13" t="n">
         <f aca="false">J13/J18</f>
-        <v>0.157894736842105</v>
+        <v>0.160869565217391</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10073,7 +11529,7 @@
       </c>
       <c r="K14" s="13" t="n">
         <f aca="false">J14/J18</f>
-        <v>0.267543859649123</v>
+        <v>0.265217391304348</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10120,10 +11576,10 @@
         <v>29</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>20</v>
@@ -10139,15 +11595,15 @@
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">C16+E16+G16</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">D16+F16+H16</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K16" s="13" t="n">
         <f aca="false">J16/J18</f>
-        <v>0.548245614035088</v>
+        <v>0.547826086956522</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10183,7 +11639,7 @@
       </c>
       <c r="K17" s="13" t="n">
         <f aca="false">J17/J18</f>
-        <v>0.0263157894736842</v>
+        <v>0.0260869565217391</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10193,19 +11649,19 @@
       <c r="B18" s="15"/>
       <c r="C18" s="9" t="n">
         <f aca="false">C13+C14+C15+C16+C17</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">D13+D14+D15+D16+D17</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">E13+E14+E15+E16+E17</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">F13+F14+F15+F16+F17</f>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">G13+G14+G15+G16+G17</f>
@@ -10217,11 +11673,11 @@
       </c>
       <c r="I18" s="9" t="n">
         <f aca="false">I13+I14+I15+I16+I17</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">J13+J14+J15+J16+J17</f>
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K18" s="16" t="n">
         <f aca="false">J18/J18</f>
@@ -10299,11 +11755,11 @@
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">SUM(D23:D32)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">SUM(E23:E32)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">SUM(F23:F32)</f>
@@ -10327,7 +11783,7 @@
       </c>
       <c r="K22" s="19" t="n">
         <f aca="false">SUM(K23:K32)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L22" s="20"/>
       <c r="M22" s="19" t="n">
@@ -10344,7 +11800,7 @@
       </c>
       <c r="P22" s="19" t="n">
         <f aca="false">SUM(P23:P32)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q22" s="19" t="n">
         <f aca="false">SUM(Q23:Q32)</f>
@@ -10352,7 +11808,7 @@
       </c>
       <c r="R22" s="19" t="n">
         <f aca="false">SUM(R23:R32)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S22" s="20"/>
     </row>
@@ -10406,7 +11862,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="23" t="str">
         <f aca="false">IF(C23&lt;=0,"품절",IF(C23&lt;=10,"부족",IF(E23=0,"판매 없음","")))</f>
@@ -10422,11 +11878,11 @@
         <v>29</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="12" t="n">
         <f aca="false">SUM(F24:K24)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -10444,7 +11900,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="7" t="n">
@@ -10457,13 +11913,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S24" s="23" t="str">
         <f aca="false">IF(C24&lt;=0,"품절",IF(C24&lt;=10,"부족",IF(E24=0,"판매 없음","")))</f>
@@ -10691,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S28" s="23" t="str">
         <f aca="false">IF(C28&lt;=0,"품절",IF(C28&lt;=10,"부족",IF(E28=0,"판매 없음","")))</f>
@@ -10937,11 +12393,11 @@
       </c>
       <c r="D33" s="19" t="n">
         <f aca="false">SUM(D34:D45)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="19" t="n">
         <f aca="false">SUM(E34:E45)</f>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="19" t="n">
         <f aca="false">SUM(F34:F45)</f>
@@ -10965,12 +12421,12 @@
       </c>
       <c r="K33" s="19" t="n">
         <f aca="false">SUM(K34:K45)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="19" t="n">
         <f aca="false">SUM(M34:M45)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33" s="19" t="n">
         <f aca="false">SUM(N34:N45)</f>
@@ -11402,11 +12858,11 @@
         <v>27</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="12" t="n">
         <f aca="false">SUM(F41:K41)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>0</v>
@@ -11424,11 +12880,11 @@
         <v>0</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="22"/>
       <c r="M41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" s="7" t="n">
         <v>0</v>
@@ -11443,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="R41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="23" t="str">
         <f aca="false">IF(C41&lt;=0,"품절",IF(C41&lt;=10,"부족",IF(E41=0,"판매 없음","")))</f>
@@ -11500,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="R42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" s="23" t="str">
         <f aca="false">IF(C42&lt;=0,"품절",IF(C42&lt;=10,"부족",IF(E42=0,"판매 없음","")))</f>
@@ -11966,19 +13422,19 @@
       </c>
       <c r="C53" s="27" t="n">
         <f aca="false">C54+C58+C70+C78+C101+C123</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D53" s="27" t="n">
         <f aca="false">D54+D58+D70+D78+D101+D123</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E53" s="27" t="n">
         <f aca="false">E54+E58+E70+E78+E101+E123</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F53" s="27" t="n">
         <f aca="false">F54+F58+F70+F78+F101+F123</f>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G53" s="27" t="n">
         <f aca="false">G54+G58+G70+G78+G101+G123</f>
@@ -11990,19 +13446,19 @@
       </c>
       <c r="I53" s="27" t="n">
         <f aca="false">I54+I58+I70+I78+I101+I123</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J53" s="27" t="n">
         <f aca="false">J54+J58+J70+J78+J101+J123</f>
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L53" s="27" t="n">
         <f aca="false">L54+L58+L70+L78+L101+L123</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M53" s="27" t="n">
         <f aca="false">M54+M58+M70+M78+M101+M123</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N53" s="27" t="n">
         <f aca="false">N54+N58+N70+N78+N101+N123</f>
@@ -12022,11 +13478,11 @@
       </c>
       <c r="R53" s="27" t="n">
         <f aca="false">R54+R58+R70+R78+R101+R123</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S53" s="27" t="n">
         <f aca="false">S54+S58+S70+S78+S101+S123</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T53" s="27" t="n">
         <f aca="false">T54+T58+T70+T78+T101+T123</f>
@@ -15864,19 +17320,19 @@
       </c>
       <c r="C123" s="31" t="n">
         <f aca="false">C124+C127</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" s="31" t="n">
         <f aca="false">D124+D127</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E123" s="31" t="n">
         <f aca="false">E124+E127</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="31" t="n">
         <f aca="false">F124+F127</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" s="31" t="n">
         <f aca="false">G124+G127</f>
@@ -15888,19 +17344,19 @@
       </c>
       <c r="I123" s="31" t="n">
         <f aca="false">I124+I127</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J123" s="31" t="n">
         <f aca="false">J124+J127</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L123" s="31" t="n">
         <f aca="false">L124+L127</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M123" s="31" t="n">
         <f aca="false">M124+M127</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N123" s="31" t="n">
         <f aca="false">N124+N127</f>
@@ -15920,11 +17376,11 @@
       </c>
       <c r="R123" s="31" t="n">
         <f aca="false">R124+R127</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S123" s="31" t="n">
         <f aca="false">S124+S127</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T123" s="31" t="n">
         <f aca="false">T124+T127</f>
@@ -16109,75 +17565,75 @@
         <v>211</v>
       </c>
       <c r="C127" s="38" t="n">
-        <f aca="false">SUM(C128:C131)</f>
+        <f aca="false">SUM(C128:C133)</f>
+        <v>3</v>
+      </c>
+      <c r="D127" s="38" t="n">
+        <f aca="false">SUM(D128:D133)</f>
+        <v>3</v>
+      </c>
+      <c r="E127" s="38" t="n">
+        <f aca="false">SUM(E128:E133)</f>
+        <v>1</v>
+      </c>
+      <c r="F127" s="38" t="n">
+        <f aca="false">SUM(F128:F133)</f>
+        <v>1</v>
+      </c>
+      <c r="G127" s="38" t="n">
+        <f aca="false">SUM(G128:G133)</f>
         <v>2</v>
       </c>
-      <c r="D127" s="38" t="n">
-        <f aca="false">SUM(D128:D131)</f>
-        <v>2</v>
-      </c>
-      <c r="E127" s="38" t="n">
-        <f aca="false">SUM(E128:E131)</f>
-        <v>0</v>
-      </c>
-      <c r="F127" s="38" t="n">
-        <f aca="false">SUM(F128:F131)</f>
-        <v>0</v>
-      </c>
-      <c r="G127" s="38" t="n">
-        <f aca="false">SUM(G128:G131)</f>
-        <v>2</v>
-      </c>
       <c r="H127" s="38" t="n">
-        <f aca="false">SUM(H128:H131)</f>
+        <f aca="false">SUM(H128:H133)</f>
         <v>16</v>
       </c>
       <c r="I127" s="38" t="n">
-        <f aca="false">SUM(I128:I131)</f>
+        <f aca="false">SUM(I128:I133)</f>
+        <v>6</v>
+      </c>
+      <c r="J127" s="38" t="n">
+        <f aca="false">SUM(J128:J133)</f>
+        <v>20</v>
+      </c>
+      <c r="L127" s="38" t="n">
+        <f aca="false">SUM(L128:L133)</f>
         <v>4</v>
       </c>
-      <c r="J127" s="38" t="n">
-        <f aca="false">SUM(J128:J131)</f>
-        <v>18</v>
-      </c>
-      <c r="L127" s="38" t="n">
-        <f aca="false">SUM(L128:L131)</f>
-        <v>3</v>
-      </c>
       <c r="M127" s="38" t="n">
-        <f aca="false">SUM(M128:M131)</f>
-        <v>12</v>
+        <f aca="false">SUM(M128:M133)</f>
+        <v>13</v>
       </c>
       <c r="N127" s="38" t="n">
-        <f aca="false">SUM(N128:N131)</f>
+        <f aca="false">SUM(N128:N133)</f>
         <v>0</v>
       </c>
       <c r="O127" s="38" t="n">
-        <f aca="false">SUM(O128:O131)</f>
+        <f aca="false">SUM(O128:O133)</f>
         <v>0</v>
       </c>
       <c r="P127" s="38" t="n">
-        <f aca="false">SUM(P128:P131)</f>
+        <f aca="false">SUM(P128:P133)</f>
         <v>0</v>
       </c>
       <c r="Q127" s="38" t="n">
-        <f aca="false">SUM(Q128:Q131)</f>
+        <f aca="false">SUM(Q128:Q133)</f>
         <v>0</v>
       </c>
       <c r="R127" s="38" t="n">
-        <f aca="false">SUM(R128:R131)</f>
-        <v>0</v>
+        <f aca="false">SUM(R128:R133)</f>
+        <v>1</v>
       </c>
       <c r="S127" s="38" t="n">
-        <f aca="false">SUM(S128:S131)</f>
-        <v>0</v>
+        <f aca="false">SUM(S128:S133)</f>
+        <v>1</v>
       </c>
       <c r="T127" s="38" t="n">
-        <f aca="false">SUM(T128:T131)</f>
+        <f aca="false">SUM(T128:T133)</f>
         <v>1</v>
       </c>
       <c r="U127" s="38" t="n">
-        <f aca="false">SUM(U128:U131)</f>
+        <f aca="false">SUM(U128:U133)</f>
         <v>6</v>
       </c>
       <c r="V127" s="39" t="s">
@@ -16348,9 +17804,91 @@
       </c>
       <c r="V131" s="11"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
+    <row r="132" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="2" collapsed="false">
+      <c r="A132" s="11" t="s">
         <v>214</v>
+      </c>
+      <c r="B132" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5" t="n">
+        <f aca="false">C132+E132+G132</f>
+        <v>1</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <f aca="false">D132+F132+H132</f>
+        <v>1</v>
+      </c>
+      <c r="L132" s="5"/>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5"/>
+      <c r="P132" s="5"/>
+      <c r="Q132" s="5"/>
+      <c r="R132" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" s="5"/>
+      <c r="U132" s="5"/>
+      <c r="V132" s="11"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="2" collapsed="false">
+      <c r="A133" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B133" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5" t="n">
+        <f aca="false">C133+E133+G133</f>
+        <v>1</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <f aca="false">D133+F133+H133</f>
+        <v>1</v>
+      </c>
+      <c r="L133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5"/>
+      <c r="P133" s="5"/>
+      <c r="Q133" s="5"/>
+      <c r="R133" s="5"/>
+      <c r="S133" s="5"/>
+      <c r="T133" s="5"/>
+      <c r="U133" s="5"/>
+      <c r="V133" s="11"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -16410,10 +17948,11 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
@@ -16421,22 +17960,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16444,31 +17987,31 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16476,13 +18019,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E6" s="40" t="n">
         <v>2300</v>
@@ -16491,16 +18034,16 @@
         <v>2300</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I6" s="42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16508,13 +18051,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>3500</v>
@@ -16523,16 +18066,16 @@
         <v>2800</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16540,41 +18083,41 @@
         <v>11</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>2500</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H8" s="41" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I8" s="42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16582,574 +18125,738 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="44" t="n">
-        <f aca="false">E13-C13</f>
-        <v>3</v>
-      </c>
-      <c r="H13" s="44" t="n">
-        <f aca="false">F13-D13</f>
         <v>10</v>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>1</v>
+      <c r="B13" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>5020</v>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>11965</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <f aca="false">IF(F13=0,0,G13/F13)</f>
+        <v>0.00384454659423318</v>
+      </c>
+      <c r="I13" s="48" t="n">
+        <f aca="false">IF(G13=0,0,J13/G13)</f>
+        <v>3369.5</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>154997</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="44" t="n">
+        <v>6140</v>
+      </c>
+      <c r="M13" s="49" t="n">
+        <f aca="false">IF(J13=0,0,L13/J13)</f>
+        <v>0.0396136699419989</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="44" t="n">
-        <f aca="false">E14-C14</f>
-        <v>3</v>
-      </c>
-      <c r="H14" s="44" t="n">
-        <f aca="false">F14-D14</f>
-        <v>7</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="44" t="n">
+        <v>4930</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5301</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <f aca="false">IF(F14=0,0,G14/F14)</f>
+        <v>0.00207508017355216</v>
+      </c>
+      <c r="I14" s="48" t="n">
+        <f aca="false">IF(G14=0,0,J14/G14)</f>
+        <v>2371.90909090909</v>
+      </c>
+      <c r="J14" s="45" t="n">
+        <v>26091</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="44" t="n">
+        <v>79750</v>
+      </c>
+      <c r="M14" s="49" t="n">
+        <f aca="false">IF(J14=0,0,L14/J14)</f>
+        <v>3.05660955885171</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="B15" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" s="44" t="n">
+        <v>5090</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E15" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>12669</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <f aca="false">IF(F15=0,0,G15/F15)</f>
+        <v>0.000789328281632331</v>
+      </c>
+      <c r="I15" s="48" t="n">
+        <f aca="false">IF(G15=0,0,J15/G15)</f>
+        <v>3607.9</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>36079</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="44" t="n">
+        <v>92400</v>
+      </c>
+      <c r="M15" s="49" t="n">
+        <f aca="false">IF(J15=0,0,L15/J15)</f>
+        <v>2.56104659220045</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="51" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>900</v>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>820</v>
+      </c>
+      <c r="G16" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="54" t="n">
+        <f aca="false">IF(F16=0,0,G16/F16)</f>
+        <v>0.00121951219512195</v>
+      </c>
+      <c r="I16" s="55" t="n">
+        <f aca="false">IF(G16=0,0,J16/G16)</f>
+        <v>829</v>
+      </c>
+      <c r="J16" s="51" t="n">
+        <v>829</v>
+      </c>
+      <c r="K16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="56" t="n">
+        <f aca="false">IF(J16=0,0,L16/J16)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="51" t="n">
+        <v>27500</v>
+      </c>
+      <c r="D17" s="51" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="53" t="n">
+        <v>108</v>
+      </c>
+      <c r="G17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="54" t="n">
+        <f aca="false">IF(F17=0,0,G17/F17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="55" t="n">
+        <f aca="false">IF(G17=0,0,J17/G17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="56" t="n">
+        <f aca="false">IF(J17=0,0,L17/J17)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="50" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="C18" s="51" t="n">
+        <v>6880</v>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>650</v>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>301</v>
+      </c>
+      <c r="G18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="54" t="n">
+        <f aca="false">IF(F18=0,0,G18/F18)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="55" t="n">
+        <f aca="false">IF(G18=0,0,J18/G18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="56" t="n">
+        <f aca="false">IF(J18=0,0,L18/J18)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="9" t="n">
+        <f aca="false">SUM(F13:F18)</f>
+        <v>31164</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <f aca="false">SUM(G13:G18)</f>
+        <v>68</v>
+      </c>
+      <c r="H19" s="58" t="n">
+        <f aca="false">IF(F19=0,0,G19/F19)</f>
+        <v>0.00218200487742267</v>
+      </c>
+      <c r="I19" s="59" t="n">
+        <f aca="false">IF(G19=0,0,J19/G19)</f>
+        <v>3205.82352941177</v>
+      </c>
+      <c r="J19" s="59" t="n">
+        <f aca="false">SUM(J13:J18)</f>
+        <v>217996</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <f aca="false">SUM(K13:K18)</f>
+        <v>5</v>
+      </c>
+      <c r="L19" s="59" t="n">
+        <f aca="false">SUM(L13:L18)</f>
+        <v>178290</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <f aca="false">IF(J19=0,0,L19/J19)</f>
+        <v>0.817859043285198</v>
+      </c>
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="60" t="n">
+        <f aca="false">E24-C24</f>
         <v>3</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="H24" s="60" t="n">
+        <f aca="false">F24-D24</f>
+        <v>10</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" s="60" t="n">
+        <f aca="false">E25-C25</f>
+        <v>3</v>
+      </c>
+      <c r="H25" s="60" t="n">
+        <f aca="false">F25-D25</f>
+        <v>7</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G15" s="44" t="n">
-        <f aca="false">E15-C15</f>
+      <c r="G26" s="60" t="n">
+        <f aca="false">E26-C26</f>
         <v>3</v>
       </c>
-      <c r="H15" s="44" t="n">
-        <f aca="false">F15-D15</f>
+      <c r="H26" s="60" t="n">
+        <f aca="false">F26-D26</f>
         <v>17</v>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="I26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="9" t="n">
-        <f aca="false">C13+C14+C15</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">D13+D14+D15</f>
+      <c r="B27" s="15"/>
+      <c r="C27" s="9" t="n">
+        <f aca="false">C24+C25+C26</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <f aca="false">D24+D25+D26</f>
         <v>5</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">E13+E14+E15</f>
+      <c r="E27" s="9" t="n">
+        <f aca="false">E24+E25+E26</f>
         <v>10</v>
       </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">F13+F14+F15</f>
+      <c r="F27" s="9" t="n">
+        <f aca="false">F24+F25+F26</f>
         <v>39</v>
       </c>
-      <c r="G16" s="45" t="n">
-        <f aca="false">G13+G14+G15</f>
+      <c r="G27" s="61" t="n">
+        <f aca="false">G24+G25+G26</f>
         <v>9</v>
       </c>
-      <c r="H16" s="45" t="n">
-        <f aca="false">H13+H14+H15</f>
+      <c r="H27" s="61" t="n">
+        <f aca="false">H24+H25+H26</f>
         <v>34</v>
       </c>
-      <c r="I16" s="9" t="n">
-        <f aca="false">I13+I14+I15</f>
+      <c r="I27" s="9" t="n">
+        <f aca="false">I24+I25+I26</f>
         <v>4</v>
       </c>
-      <c r="J16" s="9" t="n">
-        <f aca="false">J13+J14+J15</f>
+      <c r="J27" s="9" t="n">
+        <f aca="false">J24+J25+J26</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="47" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="62" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="63" t="n">
         <v>2000</v>
       </c>
-      <c r="B23" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D24" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="47" t="n">
-        <v>2300</v>
-      </c>
-      <c r="B25" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="55" t="s">
-        <v>283</v>
-      </c>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="47" t="n">
-        <v>2600</v>
-      </c>
-      <c r="B28" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="47" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B30" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E30" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C31" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D31" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="47" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B32" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="E32" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F32" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C33" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D33" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C34" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D34" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
+      <c r="B34" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F34" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C35" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D35" s="52" t="s">
-        <v>275</v>
+        <v>303</v>
+      </c>
+      <c r="C35" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="63" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B36" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E36" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="71" t="s">
+        <v>312</v>
+      </c>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D38" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="47" t="n">
-        <v>1500</v>
-      </c>
-      <c r="B39" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="49" t="s">
-        <v>271</v>
+      <c r="A39" s="63" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B39" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>239</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="E39" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>272</v>
+        <v>239</v>
+      </c>
+      <c r="E39" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F39" s="67" t="s">
+        <v>239</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
@@ -17158,44 +18865,44 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C40" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D40" s="52" t="s">
-        <v>300</v>
+        <v>318</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
-      <c r="G40" s="55" t="s">
-        <v>301</v>
-      </c>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
+      <c r="G40" s="71" t="s">
+        <v>319</v>
+      </c>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="47" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B41" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="49" t="s">
-        <v>271</v>
+      <c r="A41" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="E41" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>272</v>
+        <v>239</v>
+      </c>
+      <c r="E41" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="F41" s="67" t="s">
+        <v>239</v>
       </c>
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
@@ -17204,42 +18911,44 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C42" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D42" s="52" t="s">
-        <v>300</v>
+        <v>318</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
+      <c r="G42" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="47" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B43" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="49" t="s">
-        <v>271</v>
+      <c r="A43" s="63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="E43" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>272</v>
+        <v>321</v>
+      </c>
+      <c r="E43" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>232</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
@@ -17248,154 +18957,122 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C44" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D44" s="52" t="s">
-        <v>300</v>
+        <v>318</v>
+      </c>
+      <c r="C44" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>314</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="53"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B45" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="E45" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F45" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A45" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="68" t="s">
         <v>304</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C46" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D46" s="52" t="s">
-        <v>282</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
-      <c r="G46" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="55"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="47" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B47" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E47" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F47" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B48" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C48" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D48" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="55" t="s">
-        <v>308</v>
-      </c>
-      <c r="H48" s="55"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="55"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="11" t="s">
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B49" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C49" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D49" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
+      <c r="C49" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="47" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B50" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>237</v>
+      <c r="A50" s="63" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B50" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="65" t="s">
+        <v>300</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="E50" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F50" s="51" t="s">
-        <v>279</v>
+        <v>327</v>
+      </c>
+      <c r="E50" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F50" s="67" t="s">
+        <v>301</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
@@ -17404,44 +19081,44 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C51" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D51" s="52" t="s">
-        <v>282</v>
+        <v>318</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>329</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
-      <c r="G51" s="55" t="s">
-        <v>310</v>
-      </c>
-      <c r="H51" s="55"/>
-      <c r="I51" s="55"/>
-      <c r="J51" s="55"/>
+      <c r="G51" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="H51" s="71"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="71"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>311</v>
+      <c r="A52" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B52" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="65" t="s">
+        <v>300</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="E52" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F52" s="51" t="s">
-        <v>237</v>
+        <v>327</v>
+      </c>
+      <c r="E52" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F52" s="67" t="s">
+        <v>301</v>
       </c>
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
@@ -17450,194 +19127,198 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C53" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D53" s="52" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+      <c r="C53" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>329</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
-      <c r="G53" s="53"/>
-      <c r="H53" s="53"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="53"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B54" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D54" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="53"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B54" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E54" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F54" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C55" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="D55" s="52" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55" s="68" t="s">
+        <v>329</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
-      <c r="G55" s="55" t="s">
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="E56" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F56" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A57" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="C57" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D57" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="71"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="E58" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F58" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A59" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B59" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="H55" s="55"/>
-      <c r="I55" s="55"/>
-      <c r="J55" s="55"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="B56" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C56" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D56" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="55" t="s">
-        <v>317</v>
-      </c>
-      <c r="H56" s="55"/>
-      <c r="I56" s="55"/>
-      <c r="J56" s="55"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="n">
-        <v>4000</v>
-      </c>
-      <c r="B57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E57" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="B58" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C58" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D58" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="47" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B59" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F59" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
+      <c r="C59" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="71"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C60" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D60" s="52" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+      <c r="C60" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D60" s="68" t="s">
+        <v>311</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="53"/>
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="69"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B61" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" s="49" t="s">
-        <v>271</v>
+      <c r="A61" s="63" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B61" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>239</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="E61" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>237</v>
+        <v>308</v>
+      </c>
+      <c r="E61" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F61" s="67" t="s">
+        <v>308</v>
       </c>
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
@@ -17646,210 +19327,240 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C62" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D62" s="52" t="s">
-        <v>275</v>
+        <v>318</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>311</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="53"/>
-      <c r="I62" s="53"/>
-      <c r="J62" s="53"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B63" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C63" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D63" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="53"/>
-      <c r="I63" s="53"/>
-      <c r="J63" s="53"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="47" t="n">
-        <v>6000</v>
-      </c>
-      <c r="B64" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F64" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
+      <c r="G62" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="71"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="63" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B63" s="64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="E63" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="F63" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A64" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C64" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C65" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D65" s="52" t="s">
-        <v>275</v>
+        <v>344</v>
+      </c>
+      <c r="C65" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="53"/>
-      <c r="H65" s="53"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-    </row>
-    <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="47" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B69" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C69" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="E69" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F69" s="51" t="s">
-        <v>272</v>
-      </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B70" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C70" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D70" s="52" t="s">
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="69"/>
+      <c r="J65" s="69"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A66" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B66" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="D66" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="H66" s="71"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="71"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A67" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C67" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D67" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="71" t="s">
+        <v>346</v>
+      </c>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="71"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="63" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B68" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="F68" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A69" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C69" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="69"/>
+      <c r="H69" s="69"/>
+      <c r="I69" s="69"/>
+      <c r="J69" s="69"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B70" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="53"/>
-      <c r="I70" s="53"/>
-      <c r="J70" s="53"/>
+      <c r="D70" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F70" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="B71" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C71" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" s="52" t="s">
-        <v>300</v>
+        <v>318</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
-      <c r="G71" s="53"/>
-      <c r="H71" s="53"/>
-      <c r="I71" s="53"/>
-      <c r="J71" s="53"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="47" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B72" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>237</v>
+      <c r="A72" s="63" t="n">
+        <v>5500</v>
+      </c>
+      <c r="B72" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="65" t="s">
+        <v>300</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E72" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F72" s="51" t="s">
-        <v>230</v>
+        <v>347</v>
+      </c>
+      <c r="E72" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F72" s="67" t="s">
+        <v>239</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
@@ -17858,248 +19569,210 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B73" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C73" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D73" s="52" t="s">
-        <v>285</v>
+        <v>310</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>304</v>
       </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="53"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="47" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B74" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F74" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B75" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C75" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D75" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="55" t="s">
-        <v>328</v>
-      </c>
-      <c r="H75" s="55"/>
-      <c r="I75" s="55"/>
-      <c r="J75" s="55"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B76" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" s="20" t="s">
+      <c r="G73" s="69"/>
+      <c r="H73" s="69"/>
+      <c r="I73" s="69"/>
+      <c r="J73" s="69"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D74" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="69"/>
+      <c r="J74" s="69"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="63" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B75" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F75" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="69"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="69"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B80" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="E80" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F80" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C81" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D81" s="68" t="s">
         <v>329</v>
       </c>
-      <c r="D76" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="E76" s="50" t="s">
-        <v>330</v>
-      </c>
-      <c r="F76" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-      <c r="J76" s="20"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B77" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="C77" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="D77" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="H77" s="55"/>
-      <c r="I77" s="55"/>
-      <c r="J77" s="55"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="47" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B78" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="E78" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F78" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="B79" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C79" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D79" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="55" t="s">
-        <v>333</v>
-      </c>
-      <c r="H79" s="55"/>
-      <c r="I79" s="55"/>
-      <c r="J79" s="55"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="B80" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C80" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D80" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="H80" s="55"/>
-      <c r="I80" s="55"/>
-      <c r="J80" s="55"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="47" t="n">
-        <v>3700</v>
-      </c>
-      <c r="B81" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E81" s="50" t="s">
-        <v>330</v>
-      </c>
-      <c r="F81" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B82" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C82" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="D82" s="52" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+      <c r="C82" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D82" s="68" t="s">
+        <v>329</v>
       </c>
       <c r="E82" s="22"/>
       <c r="F82" s="22"/>
-      <c r="G82" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="H82" s="55"/>
-      <c r="I82" s="55"/>
-      <c r="J82" s="55"/>
+      <c r="G82" s="69"/>
+      <c r="H82" s="69"/>
+      <c r="I82" s="69"/>
+      <c r="J82" s="69"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="47" t="n">
-        <v>3900</v>
-      </c>
-      <c r="B83" s="48" t="n">
+      <c r="A83" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B83" s="64" t="n">
         <v>1</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E83" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="F83" s="51" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="E83" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F83" s="67" t="s">
+        <v>232</v>
       </c>
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
@@ -18108,66 +19781,316 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="C84" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="D84" s="52" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+      <c r="C84" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D84" s="68" t="s">
+        <v>314</v>
       </c>
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
-      <c r="G84" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="H84" s="55"/>
-      <c r="I84" s="55"/>
-      <c r="J84" s="55"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>337</v>
+      <c r="G84" s="69"/>
+      <c r="H84" s="69"/>
+      <c r="I84" s="69"/>
+      <c r="J84" s="69"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B85" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="E85" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F85" s="67" t="s">
+        <v>354</v>
+      </c>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="B86" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="C86" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D86" s="68" t="s">
+        <v>356</v>
+      </c>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="71" t="s">
+        <v>357</v>
+      </c>
+      <c r="H86" s="71"/>
+      <c r="I86" s="71"/>
+      <c r="J86" s="71"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="63" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B87" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="E87" s="66" t="s">
+        <v>359</v>
+      </c>
+      <c r="F87" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B88" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="C88" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="D88" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="71" t="s">
+        <v>361</v>
+      </c>
+      <c r="H88" s="71"/>
+      <c r="I88" s="71"/>
+      <c r="J88" s="71"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="63" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B89" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="E89" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F89" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="20"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B90" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D90" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="71" t="s">
+        <v>362</v>
+      </c>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="71"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A91" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B91" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D91" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="H91" s="71"/>
+      <c r="I91" s="71"/>
+      <c r="J91" s="71"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="63" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B92" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" s="66" t="s">
+        <v>359</v>
+      </c>
+      <c r="F92" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A93" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B93" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C93" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="D93" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="71" t="s">
+        <v>361</v>
+      </c>
+      <c r="H93" s="71"/>
+      <c r="I93" s="71"/>
+      <c r="J93" s="71"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="63" t="n">
+        <v>3900</v>
+      </c>
+      <c r="B94" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F94" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G94" s="20"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A95" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C95" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D95" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="H95" s="71"/>
+      <c r="I95" s="71"/>
+      <c r="J95" s="71"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G45:J45"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G49:J49"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G54:J54"/>
     <mergeCell ref="G55:J55"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G62:J62"/>
-    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G65:J65"/>
-    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G69:J69"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G77:J77"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G81:J81"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G88:J88"/>
+    <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G93:J93"/>
+    <mergeCell ref="G95:J95"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/중국라벨_판매현황_광고테스트.xlsx
+++ b/중국라벨_판매현황_광고테스트.xlsx
@@ -5808,7 +5808,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· </t>
+      <t xml:space="preserve">· 10/3~10/8, 6</t>
     </r>
     <r>
       <rPr>
@@ -5818,7 +5818,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">네이버 검색광고 리포트 </t>
+      <t xml:space="preserve">일 </t>
     </r>
     <r>
       <rPr>
@@ -5829,7 +5829,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10/8 16:57 </t>
+      <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
@@ -5839,7 +5839,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">다운로드</t>
+      <t xml:space="preserve">네이버 검색광고 리포트</t>
     </r>
     <r>
       <rPr>
@@ -6985,7 +6985,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -6994,7 +6994,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">조회 기간은 리포트 파일에 표시되지 않습니다</t>
+      <t xml:space="preserve">조회 기간 </t>
     </r>
     <r>
       <rPr>
@@ -7004,7 +7004,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">10/3~10/8). </t>
     </r>
     <r>
       <rPr>
@@ -17948,7 +17948,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -18495,95 +18495,61 @@
         <v>277</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="60" t="n">
-        <f aca="false">E24-C24</f>
-        <v>3</v>
-      </c>
-      <c r="H24" s="60" t="n">
-        <f aca="false">F24-D24</f>
-        <v>10</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G25" s="60" t="n">
         <f aca="false">E25-C25</f>
@@ -18591,21 +18557,21 @@
       </c>
       <c r="H25" s="60" t="n">
         <f aca="false">F25-D25</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>0</v>
@@ -18617,7 +18583,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G26" s="60" t="n">
         <f aca="false">E26-C26</f>
@@ -18625,207 +18591,219 @@
       </c>
       <c r="H26" s="60" t="n">
         <f aca="false">F26-D26</f>
+        <v>7</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="I26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="G27" s="60" t="n">
+        <f aca="false">E27-C27</f>
+        <v>3</v>
+      </c>
+      <c r="H27" s="60" t="n">
+        <f aca="false">F27-D27</f>
+        <v>17</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="9" t="n">
-        <f aca="false">C24+C25+C26</f>
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <f aca="false">D24+D25+D26</f>
+      <c r="B28" s="15"/>
+      <c r="C28" s="9" t="n">
+        <f aca="false">C25+C26+C27</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <f aca="false">D25+D26+D27</f>
         <v>5</v>
       </c>
-      <c r="E27" s="9" t="n">
-        <f aca="false">E24+E25+E26</f>
+      <c r="E28" s="9" t="n">
+        <f aca="false">E25+E26+E27</f>
         <v>10</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <f aca="false">F24+F25+F26</f>
+      <c r="F28" s="9" t="n">
+        <f aca="false">F25+F26+F27</f>
         <v>39</v>
       </c>
-      <c r="G27" s="61" t="n">
-        <f aca="false">G24+G25+G26</f>
+      <c r="G28" s="61" t="n">
+        <f aca="false">G25+G26+G27</f>
         <v>9</v>
       </c>
-      <c r="H27" s="61" t="n">
-        <f aca="false">H24+H25+H26</f>
+      <c r="H28" s="61" t="n">
+        <f aca="false">H25+H26+H27</f>
         <v>34</v>
       </c>
-      <c r="I27" s="9" t="n">
-        <f aca="false">I24+I25+I26</f>
+      <c r="I28" s="9" t="n">
+        <f aca="false">I25+I26+I27</f>
         <v>4</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <f aca="false">J24+J25+J26</f>
+      <c r="J28" s="9" t="n">
+        <f aca="false">J25+J26+J27</f>
         <v>8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="62" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="62" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3" t="s">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="63" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="63" t="n">
         <v>2000</v>
       </c>
-      <c r="B34" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="65" t="s">
+      <c r="B35" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D35" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="E35" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F34" s="67" t="s">
+      <c r="F35" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A36" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B36" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C36" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D35" s="68" t="s">
+      <c r="D36" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63" t="n">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="63" t="n">
         <v>2300</v>
       </c>
-      <c r="B36" s="64" t="n">
+      <c r="B37" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C37" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D37" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="E36" s="70" t="s">
+      <c r="E37" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="F36" s="67" t="s">
+      <c r="F37" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C37" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D37" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="71" t="s">
-        <v>312</v>
-      </c>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C38" s="68" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D38" s="68" t="s">
         <v>311</v>
@@ -18833,160 +18811,162 @@
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
       <c r="G38" s="71" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H38" s="71"/>
       <c r="I38" s="71"/>
       <c r="J38" s="71"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="63" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D39" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="63" t="n">
         <v>2600</v>
       </c>
-      <c r="B39" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B40" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D40" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="66" t="s">
+      <c r="E40" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F39" s="67" t="s">
+      <c r="F40" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A41" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B41" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C41" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D40" s="68" t="s">
+      <c r="D41" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="71" t="s">
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="71" t="s">
         <v>319</v>
       </c>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="63" t="n">
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="63" t="n">
         <v>2800</v>
       </c>
-      <c r="B41" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="20" t="s">
+      <c r="B42" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D42" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E41" s="70" t="s">
+      <c r="E42" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="F41" s="67" t="s">
+      <c r="F42" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="11" t="s">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A43" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="B43" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C43" s="68" t="s">
         <v>314</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D43" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="71" t="s">
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="71" t="s">
         <v>315</v>
       </c>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="71"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="63" t="n">
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="63" t="n">
         <v>3000</v>
       </c>
-      <c r="B43" s="64" t="n">
+      <c r="B44" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C44" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D44" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E44" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="F43" s="67" t="s">
+      <c r="F44" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C44" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D44" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="69"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C45" s="68" t="s">
         <v>301</v>
       </c>
       <c r="D45" s="68" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -18997,16 +18977,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B46" s="35" t="s">
         <v>310</v>
       </c>
       <c r="C46" s="68" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D46" s="68" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -19015,275 +18995,273 @@
       <c r="I46" s="69"/>
       <c r="J46" s="69"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="25" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C47" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-    </row>
-    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+    </row>
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3" t="s">
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="63" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="63" t="n">
         <v>1500</v>
       </c>
-      <c r="B50" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="65" t="s">
+      <c r="B51" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D51" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="E50" s="66" t="s">
+      <c r="E51" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F50" s="67" t="s">
+      <c r="F51" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A52" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B52" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C52" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="D52" s="68" t="s">
         <v>329</v>
       </c>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="71" t="s">
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="71" t="s">
         <v>330</v>
       </c>
-      <c r="H51" s="71"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="71"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="63" t="n">
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="71"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="63" t="n">
         <v>2000</v>
       </c>
-      <c r="B52" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="65" t="s">
+      <c r="B53" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D53" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="E52" s="66" t="s">
+      <c r="E53" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F52" s="67" t="s">
+      <c r="F53" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="11" t="s">
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A54" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B53" s="35" t="s">
+      <c r="B54" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C54" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="D54" s="68" t="s">
         <v>329</v>
       </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="69"/>
-      <c r="J53" s="69"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="63" t="n">
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="69"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="63" t="n">
         <v>2500</v>
       </c>
-      <c r="B54" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="65" t="s">
+      <c r="B55" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D55" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="E54" s="66" t="s">
+      <c r="E55" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F54" s="67" t="s">
+      <c r="F55" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="11" t="s">
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A56" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="B55" s="35" t="s">
+      <c r="B56" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C56" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D55" s="68" t="s">
+      <c r="D56" s="68" t="s">
         <v>329</v>
       </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="69"/>
-      <c r="J55" s="69"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="63" t="n">
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="69"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="63" t="n">
         <v>2800</v>
       </c>
-      <c r="B56" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="20" t="s">
+      <c r="B57" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D57" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="E56" s="66" t="s">
+      <c r="E57" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F56" s="67" t="s">
+      <c r="F57" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A57" s="11" t="s">
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A58" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B57" s="35" t="s">
+      <c r="B58" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C58" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D57" s="68" t="s">
+      <c r="D58" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="71" t="s">
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="71" t="s">
         <v>334</v>
       </c>
-      <c r="H57" s="71"/>
-      <c r="I57" s="71"/>
-      <c r="J57" s="71"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="63" t="n">
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="71"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="63" t="n">
         <v>3000</v>
       </c>
-      <c r="B58" s="64" t="n">
+      <c r="B59" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="65" t="s">
+      <c r="C59" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D59" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="E58" s="66" t="s">
+      <c r="E59" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F58" s="67" t="s">
+      <c r="F59" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A59" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="B59" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C59" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D59" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="71" t="s">
-        <v>337</v>
-      </c>
-      <c r="H59" s="71"/>
-      <c r="I59" s="71"/>
-      <c r="J59" s="71"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B60" s="35" t="s">
         <v>310</v>
@@ -19292,111 +19270,113 @@
         <v>301</v>
       </c>
       <c r="D60" s="68" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="69"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="63" t="n">
+      <c r="G60" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="H60" s="71"/>
+      <c r="I60" s="71"/>
+      <c r="J60" s="71"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A61" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="63" t="n">
         <v>3100</v>
       </c>
-      <c r="B61" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="20" t="s">
+      <c r="B62" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D62" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="E61" s="66" t="s">
+      <c r="E62" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F61" s="67" t="s">
+      <c r="F62" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="11" t="s">
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A63" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B62" s="35" t="s">
+      <c r="B63" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C62" s="68" t="s">
+      <c r="C63" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D62" s="68" t="s">
+      <c r="D63" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="71" t="s">
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="H62" s="71"/>
-      <c r="I62" s="71"/>
-      <c r="J62" s="71"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="63" t="n">
+      <c r="H63" s="71"/>
+      <c r="I63" s="71"/>
+      <c r="J63" s="71"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="63" t="n">
         <v>3500</v>
       </c>
-      <c r="B63" s="64" t="n">
+      <c r="B64" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C64" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D64" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="E63" s="70" t="s">
+      <c r="E64" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="F63" s="67" t="s">
+      <c r="F64" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="B64" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C64" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D64" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C65" s="68" t="s">
         <v>301</v>
@@ -19413,183 +19393,183 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="C66" s="68" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D66" s="68" t="s">
         <v>304</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
-      <c r="G66" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="H66" s="71"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="71"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="69"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C67" s="68" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D67" s="68" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
       <c r="G67" s="71" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="H67" s="71"/>
       <c r="I67" s="71"/>
       <c r="J67" s="71"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="63" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A68" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B68" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D68" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="71" t="s">
+        <v>346</v>
+      </c>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="71"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="63" t="n">
         <v>4000</v>
       </c>
-      <c r="B68" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="20" t="s">
+      <c r="B69" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D69" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="70" t="s">
+      <c r="E69" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="F68" s="67" t="s">
+      <c r="F69" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A69" s="11" t="s">
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A70" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B69" s="35" t="s">
+      <c r="B70" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C69" s="68" t="s">
+      <c r="C70" s="68" t="s">
         <v>314</v>
       </c>
-      <c r="D69" s="68" t="s">
+      <c r="D70" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="69"/>
-      <c r="J69" s="69"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="63" t="n">
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="69"/>
+      <c r="J70" s="69"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="63" t="n">
         <v>5000</v>
       </c>
-      <c r="B70" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="65" t="s">
+      <c r="B71" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D71" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E70" s="66" t="s">
+      <c r="E71" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F70" s="67" t="s">
+      <c r="F71" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="11" t="s">
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A72" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="B71" s="35" t="s">
+      <c r="B72" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C71" s="68" t="s">
+      <c r="C72" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D71" s="68" t="s">
+      <c r="D72" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="69"/>
-      <c r="J71" s="69"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="63" t="n">
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="69"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="69"/>
+      <c r="J72" s="69"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="63" t="n">
         <v>5500</v>
       </c>
-      <c r="B72" s="64" t="n">
+      <c r="B73" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C72" s="65" t="s">
+      <c r="C73" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="D73" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="E72" s="66" t="s">
+      <c r="E73" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F72" s="67" t="s">
+      <c r="F73" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B73" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C73" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="69"/>
-      <c r="H73" s="69"/>
-      <c r="I73" s="69"/>
-      <c r="J73" s="69"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B74" s="35" t="s">
         <v>310</v>
@@ -19607,137 +19587,137 @@
       <c r="I74" s="69"/>
       <c r="J74" s="69"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="63" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C75" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="69"/>
+      <c r="H75" s="69"/>
+      <c r="I75" s="69"/>
+      <c r="J75" s="69"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="63" t="n">
         <v>6000</v>
       </c>
-      <c r="B75" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="65" t="s">
+      <c r="B76" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D75" s="20" t="s">
+      <c r="D76" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E75" s="66" t="s">
+      <c r="E76" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F75" s="67" t="s">
+      <c r="F76" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
-      <c r="J75" s="20"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="11" t="s">
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A77" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B76" s="35" t="s">
+      <c r="B77" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C76" s="68" t="s">
+      <c r="C77" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="D76" s="68" t="s">
+      <c r="D77" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="69"/>
-      <c r="H76" s="69"/>
-      <c r="I76" s="69"/>
-      <c r="J76" s="69"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="25" t="s">
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
+      <c r="J77" s="69"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28"/>
-      <c r="J78" s="28"/>
-    </row>
-    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="28"/>
+      <c r="I79" s="28"/>
+      <c r="J79" s="28"/>
+    </row>
+    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F80" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3" t="s">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="63" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="63" t="n">
         <v>2000</v>
       </c>
-      <c r="B80" s="64" t="n">
+      <c r="B81" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C80" s="65" t="s">
+      <c r="C81" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="D80" s="20" t="s">
+      <c r="D81" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="E80" s="66" t="s">
+      <c r="E81" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="F80" s="67" t="s">
+      <c r="F81" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="20"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B81" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C81" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D81" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B82" s="35" t="s">
         <v>310</v>
@@ -19755,194 +19735,192 @@
       <c r="I82" s="69"/>
       <c r="J82" s="69"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="63" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B83" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C83" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D83" s="68" t="s">
+        <v>329</v>
+      </c>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="69"/>
+      <c r="I83" s="69"/>
+      <c r="J83" s="69"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="63" t="n">
         <v>2500</v>
       </c>
-      <c r="B83" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" s="20" t="s">
+      <c r="B84" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D83" s="20" t="s">
+      <c r="D84" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E83" s="66" t="s">
+      <c r="E84" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F83" s="67" t="s">
+      <c r="F84" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A84" s="11" t="s">
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A85" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="B84" s="35" t="s">
+      <c r="B85" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C84" s="68" t="s">
+      <c r="C85" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D84" s="68" t="s">
+      <c r="D85" s="68" t="s">
         <v>314</v>
       </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="69"/>
-      <c r="H84" s="69"/>
-      <c r="I84" s="69"/>
-      <c r="J84" s="69"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="63" t="n">
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="69"/>
+      <c r="H85" s="69"/>
+      <c r="I85" s="69"/>
+      <c r="J85" s="69"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="63" t="n">
         <v>2800</v>
       </c>
-      <c r="B85" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="20" t="s">
+      <c r="B86" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D85" s="20" t="s">
+      <c r="D86" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="E85" s="66" t="s">
+      <c r="E86" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F85" s="67" t="s">
+      <c r="F86" s="67" t="s">
         <v>354</v>
       </c>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="20"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="11" t="s">
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A87" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B86" s="35" t="s">
+      <c r="B87" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C86" s="68" t="s">
+      <c r="C87" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D86" s="68" t="s">
+      <c r="D87" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
-      <c r="G86" s="71" t="s">
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="71" t="s">
         <v>357</v>
       </c>
-      <c r="H86" s="71"/>
-      <c r="I86" s="71"/>
-      <c r="J86" s="71"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="63" t="n">
+      <c r="H87" s="71"/>
+      <c r="I87" s="71"/>
+      <c r="J87" s="71"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="63" t="n">
         <v>3100</v>
       </c>
-      <c r="B87" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="20" t="s">
+      <c r="B88" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D88" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="E87" s="66" t="s">
+      <c r="E88" s="66" t="s">
         <v>359</v>
       </c>
-      <c r="F87" s="67" t="s">
+      <c r="F88" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="20"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="11" t="s">
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A89" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B88" s="35" t="s">
+      <c r="B89" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C88" s="68" t="s">
+      <c r="C89" s="68" t="s">
         <v>324</v>
       </c>
-      <c r="D88" s="68" t="s">
+      <c r="D89" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="71" t="s">
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="71" t="s">
         <v>361</v>
       </c>
-      <c r="H88" s="71"/>
-      <c r="I88" s="71"/>
-      <c r="J88" s="71"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="63" t="n">
+      <c r="H89" s="71"/>
+      <c r="I89" s="71"/>
+      <c r="J89" s="71"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="63" t="n">
         <v>3500</v>
       </c>
-      <c r="B89" s="64" t="n">
+      <c r="B90" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C90" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="D89" s="20" t="s">
+      <c r="D90" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="E89" s="66" t="s">
+      <c r="E90" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F89" s="67" t="s">
+      <c r="F90" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G89" s="20"/>
-      <c r="H89" s="20"/>
-      <c r="I89" s="20"/>
-      <c r="J89" s="20"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="B90" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C90" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D90" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E90" s="22"/>
-      <c r="F90" s="22"/>
-      <c r="G90" s="71" t="s">
-        <v>362</v>
-      </c>
-      <c r="H90" s="71"/>
-      <c r="I90" s="71"/>
-      <c r="J90" s="71"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C91" s="68" t="s">
         <v>304</v>
@@ -19953,144 +19931,166 @@
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
       <c r="G91" s="71" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H91" s="71"/>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="63" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A92" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B92" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="D92" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="H92" s="71"/>
+      <c r="I92" s="71"/>
+      <c r="J92" s="71"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="63" t="n">
         <v>3700</v>
       </c>
-      <c r="B92" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="20" t="s">
+      <c r="B93" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="D92" s="20" t="s">
+      <c r="D93" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E92" s="66" t="s">
+      <c r="E93" s="66" t="s">
         <v>359</v>
       </c>
-      <c r="F92" s="67" t="s">
+      <c r="F93" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
-      <c r="J92" s="20"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A93" s="11" t="s">
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A94" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B93" s="35" t="s">
+      <c r="B94" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C93" s="68" t="s">
+      <c r="C94" s="68" t="s">
         <v>324</v>
       </c>
-      <c r="D93" s="68" t="s">
+      <c r="D94" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="71" t="s">
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="71" t="s">
         <v>361</v>
       </c>
-      <c r="H93" s="71"/>
-      <c r="I93" s="71"/>
-      <c r="J93" s="71"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="63" t="n">
+      <c r="H94" s="71"/>
+      <c r="I94" s="71"/>
+      <c r="J94" s="71"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="63" t="n">
         <v>3900</v>
       </c>
-      <c r="B94" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="20" t="s">
+      <c r="B95" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D94" s="20" t="s">
+      <c r="D95" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E94" s="66" t="s">
+      <c r="E95" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="F94" s="67" t="s">
+      <c r="F95" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G94" s="20"/>
-      <c r="H94" s="20"/>
-      <c r="I94" s="20"/>
-      <c r="J94" s="20"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A95" s="11" t="s">
+      <c r="G95" s="20"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A96" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="B95" s="35" t="s">
+      <c r="B96" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="C95" s="68" t="s">
+      <c r="C96" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="D95" s="68" t="s">
+      <c r="D96" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="E95" s="22"/>
-      <c r="F95" s="22"/>
-      <c r="G95" s="71" t="s">
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="71" t="s">
         <v>363</v>
       </c>
-      <c r="H95" s="71"/>
-      <c r="I95" s="71"/>
-      <c r="J95" s="71"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+      <c r="H96" s="71"/>
+      <c r="I96" s="71"/>
+      <c r="J96" s="71"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>366</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G36:J36"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G43:J43"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="G57:J57"/>
-    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G58:J58"/>
     <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G62:J62"/>
-    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G63:J63"/>
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="G66:J66"/>
     <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G71:J71"/>
-    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G68:J68"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G72:J72"/>
     <mergeCell ref="G74:J74"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="G77:J77"/>
     <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G84:J84"/>
-    <mergeCell ref="G86:J86"/>
-    <mergeCell ref="G88:J88"/>
-    <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G89:J89"/>
     <mergeCell ref="G91:J91"/>
-    <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G95:J95"/>
+    <mergeCell ref="G92:J92"/>
+    <mergeCell ref="G94:J94"/>
+    <mergeCell ref="G96:J96"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/중국라벨_판매현황_광고테스트.xlsx
+++ b/중국라벨_판매현황_광고테스트.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="368">
   <si>
     <r>
       <rPr>
@@ -7062,6 +7062,150 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하루 평균 광고비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라벨 광고 상품 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) = 217,167</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 ≈ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일이면 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">109</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 원</t>
     </r>
   </si>
   <si>
@@ -17948,7 +18092,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -18495,61 +18639,100 @@
         <v>277</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>286</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="60" t="n">
+        <f aca="false">E24-C24</f>
+        <v>3</v>
+      </c>
+      <c r="H24" s="60" t="n">
+        <f aca="false">F24-D24</f>
+        <v>10</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G25" s="60" t="n">
         <f aca="false">E25-C25</f>
@@ -18557,21 +18740,21 @@
       </c>
       <c r="H25" s="60" t="n">
         <f aca="false">F25-D25</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>0</v>
@@ -18583,7 +18766,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G26" s="60" t="n">
         <f aca="false">E26-C26</f>
@@ -18591,382 +18774,368 @@
       </c>
       <c r="H26" s="60" t="n">
         <f aca="false">F26-D26</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G27" s="60" t="n">
-        <f aca="false">E27-C27</f>
-        <v>3</v>
-      </c>
-      <c r="H27" s="60" t="n">
-        <f aca="false">F27-D27</f>
-        <v>17</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>0</v>
+      <c r="A27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="9" t="n">
+        <f aca="false">C24+C25+C26</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <f aca="false">D24+D25+D26</f>
+        <v>5</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <f aca="false">E24+E25+E26</f>
+        <v>10</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <f aca="false">F24+F25+F26</f>
+        <v>39</v>
+      </c>
+      <c r="G27" s="61" t="n">
+        <f aca="false">G24+G25+G26</f>
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="n">
+        <f aca="false">H24+H25+H26</f>
+        <v>34</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <f aca="false">I24+I25+I26</f>
+        <v>4</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <f aca="false">J24+J25+J26</f>
+        <v>8</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="9" t="n">
-        <f aca="false">C25+C26+C27</f>
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <f aca="false">D25+D26+D27</f>
-        <v>5</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <f aca="false">E25+E26+E27</f>
-        <v>10</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <f aca="false">F25+F26+F27</f>
-        <v>39</v>
-      </c>
-      <c r="G28" s="61" t="n">
-        <f aca="false">G25+G26+G27</f>
-        <v>9</v>
-      </c>
-      <c r="H28" s="61" t="n">
-        <f aca="false">H25+H26+H27</f>
-        <v>34</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <f aca="false">I25+I26+I27</f>
-        <v>4</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <f aca="false">J25+J26+J27</f>
-        <v>8</v>
+      <c r="A28" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="62" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="A29" s="62" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="63" t="n">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="63" t="n">
         <v>2000</v>
       </c>
-      <c r="B35" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D35" s="20" t="s">
+      <c r="B34" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E35" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F35" s="67" t="s">
+      <c r="E34" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F34" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="11" t="s">
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="68" t="s">
         <v>302</v>
       </c>
-      <c r="B36" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="C36" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="63" t="n">
+      <c r="D35" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="63" t="n">
         <v>2300</v>
       </c>
-      <c r="B37" s="64" t="n">
+      <c r="B36" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C36" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="E36" s="70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E37" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="F37" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
+      <c r="D37" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C38" s="68" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D38" s="68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
       <c r="G38" s="71" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H38" s="71"/>
       <c r="I38" s="71"/>
       <c r="J38" s="71"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A39" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B39" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="C39" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="D39" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="71" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="63" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B39" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F39" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" s="70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F41" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A42" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C42" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="63" t="n">
-        <v>2600</v>
-      </c>
-      <c r="B40" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E40" s="66" t="s">
+      <c r="D42" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="71" t="s">
         <v>316</v>
       </c>
-      <c r="F40" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B41" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C41" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="71" t="s">
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="E43" s="70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A44" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B44" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="63" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B42" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E42" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="F42" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C43" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="D43" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="71" t="s">
+      <c r="C44" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D44" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="63" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B44" s="64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="E44" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="F44" s="67" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C45" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D45" s="68" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -18977,16 +19146,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C46" s="68" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D46" s="68" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -18995,394 +19164,394 @@
       <c r="I46" s="69"/>
       <c r="J46" s="69"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C47" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="D47" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-    </row>
-    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="63" t="n">
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="63" t="n">
         <v>1500</v>
       </c>
-      <c r="B51" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="E51" s="66" t="s">
+      <c r="B50" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="F51" s="67" t="s">
+      <c r="D50" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="E50" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F50" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A51" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="H51" s="71"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="71"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B52" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A52" s="11" t="s">
+      <c r="D52" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="B52" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C52" s="68" t="s">
+      <c r="E52" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A53" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C53" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B54" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="D52" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="71" t="s">
+      <c r="D54" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="E54" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F54" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A55" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D55" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="63" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B53" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="E53" s="66" t="s">
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E56" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F56" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A57" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C57" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D57" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="71"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="F53" s="67" t="s">
-        <v>301</v>
-      </c>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B54" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D54" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="69"/>
-      <c r="H54" s="69"/>
-      <c r="I54" s="69"/>
-      <c r="J54" s="69"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="63" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B55" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="E55" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F55" s="67" t="s">
-        <v>301</v>
-      </c>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B56" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C56" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D56" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="69"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="63" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B57" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="20" t="s">
+      <c r="D58" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="E58" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F58" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="D57" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="E57" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F57" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="B58" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C58" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D58" s="68" t="s">
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A59" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B59" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="71" t="s">
-        <v>334</v>
-      </c>
-      <c r="H58" s="71"/>
-      <c r="I58" s="71"/>
-      <c r="J58" s="71"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="63" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B59" s="64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="E59" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F59" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
+      <c r="C59" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="71" t="s">
+        <v>338</v>
+      </c>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="71"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C60" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D60" s="68" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
-      <c r="G60" s="71" t="s">
-        <v>337</v>
-      </c>
-      <c r="H60" s="71"/>
-      <c r="I60" s="71"/>
-      <c r="J60" s="71"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A61" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B61" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C61" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D61" s="68" t="s">
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="69"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="63" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B61" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E61" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F61" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A62" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="71"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="63" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B63" s="64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="E63" s="70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F63" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A64" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="B64" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="63" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B62" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="E62" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F62" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B63" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C63" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D63" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="H63" s="71"/>
-      <c r="I63" s="71"/>
-      <c r="J63" s="71"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="63" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B64" s="64" t="n">
-        <v>4</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="E64" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="F64" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
+      <c r="C64" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="C65" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
@@ -19393,192 +19562,192 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="C66" s="68" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="D66" s="68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
+      <c r="G66" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="H66" s="71"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="71"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C67" s="68" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D67" s="68" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
       <c r="G67" s="71" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="H67" s="71"/>
       <c r="I67" s="71"/>
       <c r="J67" s="71"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A68" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B68" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="C68" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="D68" s="68" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="63" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B68" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F68" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A69" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B69" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="71" t="s">
-        <v>346</v>
-      </c>
-      <c r="H68" s="71"/>
-      <c r="I68" s="71"/>
-      <c r="J68" s="71"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="63" t="n">
-        <v>4000</v>
-      </c>
-      <c r="B69" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D69" s="20" t="s">
+      <c r="C69" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="69"/>
+      <c r="H69" s="69"/>
+      <c r="I69" s="69"/>
+      <c r="J69" s="69"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B70" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="D70" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E69" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="F69" s="67" t="s">
+      <c r="E70" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F70" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B70" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C70" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="D70" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="69"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="63" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B71" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D71" s="20" t="s">
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D71" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="63" t="n">
+        <v>5500</v>
+      </c>
+      <c r="B72" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E72" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F72" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="E71" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F71" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B72" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C72" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D72" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="63" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B73" s="64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D73" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="E73" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F73" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="69"/>
+      <c r="H73" s="69"/>
+      <c r="I73" s="69"/>
+      <c r="J73" s="69"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C74" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D74" s="68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
@@ -19587,146 +19756,146 @@
       <c r="I74" s="69"/>
       <c r="J74" s="69"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B75" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C75" s="68" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="63" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B75" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="D75" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="69"/>
-      <c r="H75" s="69"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="69"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="63" t="n">
-        <v>6000</v>
-      </c>
-      <c r="B76" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" s="65" t="s">
+      <c r="D75" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F75" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="69"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="69"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D76" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E76" s="66" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B80" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="F76" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-      <c r="J76" s="20"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B77" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C77" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D77" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="69"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="69"/>
-      <c r="J77" s="69"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="B79" s="28"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="28"/>
-      <c r="J79" s="28"/>
-    </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="63" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B81" s="64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C81" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="E81" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="F81" s="67" t="s">
-        <v>301</v>
-      </c>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
+      <c r="D80" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="E80" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="F80" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C81" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="D81" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B82" s="35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C82" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D82" s="68" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E82" s="22"/>
       <c r="F82" s="22"/>
@@ -19735,362 +19904,342 @@
       <c r="I82" s="69"/>
       <c r="J82" s="69"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="11" t="s">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B83" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F83" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B84" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C84" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D84" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="69"/>
+      <c r="H84" s="69"/>
+      <c r="I84" s="69"/>
+      <c r="J84" s="69"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="63" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B85" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="E85" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F85" s="67" t="s">
+        <v>355</v>
+      </c>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B86" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C86" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D86" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="71" t="s">
+        <v>358</v>
+      </c>
+      <c r="H86" s="71"/>
+      <c r="I86" s="71"/>
+      <c r="J86" s="71"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="63" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B87" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E87" s="66" t="s">
+        <v>360</v>
+      </c>
+      <c r="F87" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="B88" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C88" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="B83" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C83" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D83" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="69"/>
-      <c r="H83" s="69"/>
-      <c r="I83" s="69"/>
-      <c r="J83" s="69"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="63" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B84" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="20" t="s">
+      <c r="D88" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="71" t="s">
+        <v>362</v>
+      </c>
+      <c r="H88" s="71"/>
+      <c r="I88" s="71"/>
+      <c r="J88" s="71"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="63" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B89" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E89" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F89" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="E84" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F84" s="67" t="s">
-        <v>232</v>
-      </c>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A85" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B85" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C85" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D85" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
-      <c r="G85" s="69"/>
-      <c r="H85" s="69"/>
-      <c r="I85" s="69"/>
-      <c r="J85" s="69"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="63" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B86" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="E86" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F86" s="67" t="s">
-        <v>354</v>
-      </c>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="20"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B87" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C87" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D87" s="68" t="s">
-        <v>356</v>
-      </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="71" t="s">
-        <v>357</v>
-      </c>
-      <c r="H87" s="71"/>
-      <c r="I87" s="71"/>
-      <c r="J87" s="71"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="63" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B88" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="E88" s="66" t="s">
-        <v>359</v>
-      </c>
-      <c r="F88" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B89" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="C89" s="68" t="s">
-        <v>324</v>
-      </c>
-      <c r="D89" s="68" t="s">
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="20"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B90" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
-      <c r="G89" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="H89" s="71"/>
-      <c r="I89" s="71"/>
-      <c r="J89" s="71"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="63" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B90" s="64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="E90" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F90" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
+      <c r="C90" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D90" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="71"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C91" s="68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
       <c r="G91" s="71" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H91" s="71"/>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A92" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B92" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="C92" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D92" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="71" t="s">
-        <v>363</v>
-      </c>
-      <c r="H92" s="71"/>
-      <c r="I92" s="71"/>
-      <c r="J92" s="71"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="63" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="63" t="n">
         <v>3700</v>
       </c>
-      <c r="B93" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="D93" s="20" t="s">
+      <c r="B92" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="D92" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="66" t="s">
-        <v>359</v>
-      </c>
-      <c r="F93" s="67" t="s">
+      <c r="E92" s="66" t="s">
+        <v>360</v>
+      </c>
+      <c r="F92" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A94" s="11" t="s">
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A93" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B93" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C93" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="D93" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="71" t="s">
+        <v>362</v>
+      </c>
+      <c r="H93" s="71"/>
+      <c r="I93" s="71"/>
+      <c r="J93" s="71"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="63" t="n">
+        <v>3900</v>
+      </c>
+      <c r="B94" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F94" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="G94" s="20"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A95" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B95" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C95" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D95" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="71" t="s">
         <v>364</v>
       </c>
-      <c r="B94" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C94" s="68" t="s">
-        <v>324</v>
-      </c>
-      <c r="D94" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-      <c r="G94" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="H94" s="71"/>
-      <c r="I94" s="71"/>
-      <c r="J94" s="71"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="63" t="n">
-        <v>3900</v>
-      </c>
-      <c r="B95" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D95" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E95" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F95" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
-      <c r="I95" s="20"/>
-      <c r="J95" s="20"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A96" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B96" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="C96" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="D96" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="71" t="s">
-        <v>363</v>
-      </c>
-      <c r="H96" s="71"/>
-      <c r="I96" s="71"/>
-      <c r="J96" s="71"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>366</v>
+      <c r="H95" s="71"/>
+      <c r="I95" s="71"/>
+      <c r="J95" s="71"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G37:J37"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G61:J61"/>
-    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="G66:J66"/>
     <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G68:J68"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="G69:J69"/>
+    <mergeCell ref="G71:J71"/>
+    <mergeCell ref="G73:J73"/>
     <mergeCell ref="G74:J74"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G81:J81"/>
     <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G85:J85"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G88:J88"/>
+    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G91:J91"/>
-    <mergeCell ref="G92:J92"/>
-    <mergeCell ref="G94:J94"/>
-    <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G93:J93"/>
+    <mergeCell ref="G95:J95"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
